--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-03-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-03-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L10"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>רני רחמים - עכשיו זה נגמר</v>
+        <v>קורין מלאכי - ברוקלין</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-22</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410122&amp;sid=06f082ce2a005a517b85ff28f7c5070e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410131&amp;sid=aeee673ef85eaa94cbe951d99c786ab8</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>רני רחמים - עכשיו זה נגמר</v>
+        <v>קורין מלאכי - ברוקלין</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>רגב הוד - תודה לאל קאבר</v>
+        <v>מנחם שוקרון - תפילות</v>
       </c>
       <c r="B3" t="str">
         <v>2026-03-22</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410121&amp;sid=06f082ce2a005a517b85ff28f7c5070e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410130&amp;sid=aeee673ef85eaa94cbe951d99c786ab8</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>רגב הוד - תודה לאל קאבר</v>
+        <v>מנחם שוקרון - תפילות</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>נתי גדמו - כל מה שבניתי</v>
+        <v>יניב יעקובי - שירת הים</v>
       </c>
       <c r="B4" t="str">
         <v>2026-03-22</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410120&amp;sid=06f082ce2a005a517b85ff28f7c5070e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410129&amp;sid=aeee673ef85eaa94cbe951d99c786ab8</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>נתי גדמו - כל מה שבניתי</v>
+        <v>יניב יעקובי - שירת הים</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>נהוראי אריאלי - זהות בדויה</v>
+        <v>יוסף יצחק פרקש - אל תירא</v>
       </c>
       <c r="B5" t="str">
         <v>2026-03-22</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410119&amp;sid=06f082ce2a005a517b85ff28f7c5070e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410128&amp;sid=aeee673ef85eaa94cbe951d99c786ab8</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>נהוראי אריאלי - זהות בדויה</v>
+        <v>יוסף יצחק פרקש - אל תירא</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>לידור - כל מה שעשיתי</v>
+        <v>יואל אלהרר &amp; שמואל אלהרר - רבינו</v>
       </c>
       <c r="B6" t="str">
         <v>2026-03-22</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410118&amp;sid=06f082ce2a005a517b85ff28f7c5070e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410127&amp;sid=aeee673ef85eaa94cbe951d99c786ab8</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -621,21 +621,21 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>לידור - כל מה שעשיתי</v>
+        <v>יואל אלהרר &amp; שמואל אלהרר - רבינו</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>יותם רכס - עסקים כרגיל</v>
+        <v>טל עזאני - מלכת הלבבות</v>
       </c>
       <c r="B7" t="str">
         <v>2026-03-22</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410117&amp;sid=06f082ce2a005a517b85ff28f7c5070e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410126&amp;sid=aeee673ef85eaa94cbe951d99c786ab8</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -659,21 +659,21 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>יותם רכס - עסקים כרגיל</v>
+        <v>טל עזאני - מלכת הלבבות</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>בן צור - אישתי</v>
+        <v>אליעד לוי - געגוע אלייך</v>
       </c>
       <c r="B8" t="str">
         <v>2026-03-22</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410116&amp;sid=06f082ce2a005a517b85ff28f7c5070e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410125&amp;sid=aeee673ef85eaa94cbe951d99c786ab8</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -697,21 +697,21 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>בן צור - אישתי</v>
+        <v>אליעד לוי - געגוע אלייך</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>אתל - טוקסיק</v>
+        <v>אבי חן - לחזור לבית</v>
       </c>
       <c r="B9" t="str">
         <v>2026-03-22</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410115&amp;sid=06f082ce2a005a517b85ff28f7c5070e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410124&amp;sid=aeee673ef85eaa94cbe951d99c786ab8</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -735,21 +735,21 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>אתל - טוקסיק</v>
+        <v>אבי חן - לחזור לבית</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>ארי ברמן - דור הגאולה</v>
+        <v>שר שלום מהצרי - והיא שעמדה</v>
       </c>
       <c r="B10" t="str">
         <v>2026-03-22</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410114&amp;sid=06f082ce2a005a517b85ff28f7c5070e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410123&amp;sid=aeee673ef85eaa94cbe951d99c786ab8</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -773,88 +773,12 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>ארי ברמן - דור הגאולה</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>אלה הודיה גוילי - סוף העולם</v>
-      </c>
-      <c r="B11" t="str">
-        <v>2026-03-22</v>
-      </c>
-      <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410113&amp;sid=06f082ce2a005a517b85ff28f7c5070e</v>
-      </c>
-      <c r="D11" t="str">
-        <v>2026-03-22</v>
-      </c>
-      <c r="E11" t="str">
-        <v/>
-      </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
-      <c r="G11" t="str">
-        <v/>
-      </c>
-      <c r="H11" t="str">
-        <v/>
-      </c>
-      <c r="I11" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J11" t="str">
-        <v/>
-      </c>
-      <c r="K11" t="str">
-        <v/>
-      </c>
-      <c r="L11" t="str">
-        <v>אלה הודיה גוילי - סוף העולם</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>אדל חן - אושר אמיתי</v>
-      </c>
-      <c r="B12" t="str">
-        <v>2026-03-22</v>
-      </c>
-      <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410112&amp;sid=06f082ce2a005a517b85ff28f7c5070e</v>
-      </c>
-      <c r="D12" t="str">
-        <v>2026-03-22</v>
-      </c>
-      <c r="E12" t="str">
-        <v/>
-      </c>
-      <c r="F12" t="str">
-        <v/>
-      </c>
-      <c r="G12" t="str">
-        <v/>
-      </c>
-      <c r="H12" t="str">
-        <v/>
-      </c>
-      <c r="I12" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J12" t="str">
-        <v/>
-      </c>
-      <c r="K12" t="str">
-        <v/>
-      </c>
-      <c r="L12" t="str">
-        <v>אדל חן - אושר אמיתי</v>
+        <v>שר שלום מהצרי - והיא שעמדה</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L10"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-03-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-03-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L12"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>קורין מלאכי - ברוקלין</v>
+        <v>שירה זלוף - הפסקה</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410131&amp;sid=aeee673ef85eaa94cbe951d99c786ab8</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410142&amp;sid=0d8343258330d16e696614b7e3125352</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-23</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>קורין מלאכי - ברוקלין</v>
+        <v>שירה זלוף - הפסקה</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>מנחם שוקרון - תפילות</v>
+        <v>שיר זוארץ - אוטוטו</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410130&amp;sid=aeee673ef85eaa94cbe951d99c786ab8</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410141&amp;sid=0d8343258330d16e696614b7e3125352</v>
       </c>
       <c r="D3" t="str">
         <v>2026-03-23</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>מנחם שוקרון - תפילות</v>
+        <v>שיר זוארץ - אוטוטו</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>יניב יעקובי - שירת הים</v>
+        <v>רון פרץ - פול מון</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410129&amp;sid=aeee673ef85eaa94cbe951d99c786ab8</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410140&amp;sid=0d8343258330d16e696614b7e3125352</v>
       </c>
       <c r="D4" t="str">
         <v>2026-03-23</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>יניב יעקובי - שירת הים</v>
+        <v>רון פרץ - פול מון</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>יוסף יצחק פרקש - אל תירא</v>
+        <v>עידו בן דב &amp; ארי &amp; יורגן - עוד שוט</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410128&amp;sid=aeee673ef85eaa94cbe951d99c786ab8</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410139&amp;sid=0d8343258330d16e696614b7e3125352</v>
       </c>
       <c r="D5" t="str">
         <v>2026-03-23</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>יוסף יצחק פרקש - אל תירא</v>
+        <v>עידו בן דב &amp; ארי &amp; יורגן - עוד שוט</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>יואל אלהרר &amp; שמואל אלהרר - רבינו</v>
+        <v>נמואל - יום בא</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410127&amp;sid=aeee673ef85eaa94cbe951d99c786ab8</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410138&amp;sid=0d8343258330d16e696614b7e3125352</v>
       </c>
       <c r="D6" t="str">
         <v>2026-03-23</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>יואל אלהרר &amp; שמואל אלהרר - רבינו</v>
+        <v>נמואל - יום בא</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>טל עזאני - מלכת הלבבות</v>
+        <v>מירב ארז - אלף לילה</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410126&amp;sid=aeee673ef85eaa94cbe951d99c786ab8</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410137&amp;sid=0d8343258330d16e696614b7e3125352</v>
       </c>
       <c r="D7" t="str">
         <v>2026-03-23</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>טל עזאני - מלכת הלבבות</v>
+        <v>מירב ארז - אלף לילה</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>אליעד לוי - געגוע אלייך</v>
+        <v>ליר - לא באמת כואב</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410125&amp;sid=aeee673ef85eaa94cbe951d99c786ab8</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410136&amp;sid=0d8343258330d16e696614b7e3125352</v>
       </c>
       <c r="D8" t="str">
         <v>2026-03-23</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>אליעד לוי - געגוע אלייך</v>
+        <v>ליר - לא באמת כואב</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>אבי חן - לחזור לבית</v>
+        <v>יערה לוי - קיטשי</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410124&amp;sid=aeee673ef85eaa94cbe951d99c786ab8</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410135&amp;sid=0d8343258330d16e696614b7e3125352</v>
       </c>
       <c r="D9" t="str">
         <v>2026-03-23</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>אבי חן - לחזור לבית</v>
+        <v>יערה לוי - קיטשי</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>שר שלום מהצרי - והיא שעמדה</v>
+        <v>ינון טייב - גור אריה יהודה</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-03-22</v>
+        <v>2026-03-23</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410123&amp;sid=aeee673ef85eaa94cbe951d99c786ab8</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410134&amp;sid=0d8343258330d16e696614b7e3125352</v>
       </c>
       <c r="D10" t="str">
         <v>2026-03-23</v>
@@ -773,12 +773,88 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>שר שלום מהצרי - והיא שעמדה</v>
+        <v>ינון טייב - גור אריה יהודה</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>יוסף ממיה - דרכה של תורה</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-03-23</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410133&amp;sid=0d8343258330d16e696614b7e3125352</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-03-23</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>יוסף ממיה - דרכה של תורה</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>אביה שרמן - ציון</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-03-23</v>
+      </c>
+      <c r="C12" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410132&amp;sid=0d8343258330d16e696614b7e3125352</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-03-23</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>אביה שרמן - ציון</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L12"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-03-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-03-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שירה זלוף - הפסקה</v>
+        <v>רועי בנטין - ציפורים</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-23</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410142&amp;sid=0d8343258330d16e696614b7e3125352</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410143&amp;sid=416d2de173a9fe843e6a9b7d81d0dd34</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,392 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שירה זלוף - הפסקה</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>שיר זוארץ - אוטוטו</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-03-23</v>
-      </c>
-      <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410141&amp;sid=0d8343258330d16e696614b7e3125352</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-03-23</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>שיר זוארץ - אוטוטו</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>רון פרץ - פול מון</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-03-23</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410140&amp;sid=0d8343258330d16e696614b7e3125352</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-03-23</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>רון פרץ - פול מון</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>עידו בן דב &amp; ארי &amp; יורגן - עוד שוט</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-03-23</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410139&amp;sid=0d8343258330d16e696614b7e3125352</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-03-23</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>עידו בן דב &amp; ארי &amp; יורגן - עוד שוט</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>נמואל - יום בא</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-03-23</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410138&amp;sid=0d8343258330d16e696614b7e3125352</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-03-23</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>נמואל - יום בא</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>מירב ארז - אלף לילה</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-03-23</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410137&amp;sid=0d8343258330d16e696614b7e3125352</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-03-23</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>מירב ארז - אלף לילה</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>ליר - לא באמת כואב</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-03-23</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410136&amp;sid=0d8343258330d16e696614b7e3125352</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-03-23</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>ליר - לא באמת כואב</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>יערה לוי - קיטשי</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-03-23</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410135&amp;sid=0d8343258330d16e696614b7e3125352</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-03-23</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>יערה לוי - קיטשי</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>ינון טייב - גור אריה יהודה</v>
-      </c>
-      <c r="B10" t="str">
-        <v>2026-03-23</v>
-      </c>
-      <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410134&amp;sid=0d8343258330d16e696614b7e3125352</v>
-      </c>
-      <c r="D10" t="str">
-        <v>2026-03-23</v>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
-        <v>ינון טייב - גור אריה יהודה</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>יוסף ממיה - דרכה של תורה</v>
-      </c>
-      <c r="B11" t="str">
-        <v>2026-03-23</v>
-      </c>
-      <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410133&amp;sid=0d8343258330d16e696614b7e3125352</v>
-      </c>
-      <c r="D11" t="str">
-        <v>2026-03-23</v>
-      </c>
-      <c r="E11" t="str">
-        <v/>
-      </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
-      <c r="G11" t="str">
-        <v/>
-      </c>
-      <c r="H11" t="str">
-        <v/>
-      </c>
-      <c r="I11" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J11" t="str">
-        <v/>
-      </c>
-      <c r="K11" t="str">
-        <v/>
-      </c>
-      <c r="L11" t="str">
-        <v>יוסף ממיה - דרכה של תורה</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>אביה שרמן - ציון</v>
-      </c>
-      <c r="B12" t="str">
-        <v>2026-03-23</v>
-      </c>
-      <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410132&amp;sid=0d8343258330d16e696614b7e3125352</v>
-      </c>
-      <c r="D12" t="str">
-        <v>2026-03-23</v>
-      </c>
-      <c r="E12" t="str">
-        <v/>
-      </c>
-      <c r="F12" t="str">
-        <v/>
-      </c>
-      <c r="G12" t="str">
-        <v/>
-      </c>
-      <c r="H12" t="str">
-        <v/>
-      </c>
-      <c r="I12" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J12" t="str">
-        <v/>
-      </c>
-      <c r="K12" t="str">
-        <v/>
-      </c>
-      <c r="L12" t="str">
-        <v>אביה שרמן - ציון</v>
+        <v>רועי בנטין - ציפורים</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-03-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-03-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>רועי בנטין - ציפורים</v>
+        <v>הודיה ויצמן - עכשיו בסדר</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-23</v>
+        <v>2026-03-24</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410143&amp;sid=416d2de173a9fe843e6a9b7d81d0dd34</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410149&amp;sid=8b258206d76373ed616ca34a422be80f</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-24</v>
@@ -469,12 +469,164 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>רועי בנטין - ציפורים</v>
+        <v>הודיה ויצמן - עכשיו בסדר</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>אפיק מרחום - איתך הייתי פורח</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-03-24</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410148&amp;sid=8b258206d76373ed616ca34a422be80f</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-03-24</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>אפיק מרחום - איתך הייתי פורח</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>אלי וינר - אף פעם לא לבד</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-03-24</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410147&amp;sid=8b258206d76373ed616ca34a422be80f</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-03-24</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>אלי וינר - אף פעם לא לבד</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>אופק יפרח אזולאי - עלם חמודות</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-03-24</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410146&amp;sid=8b258206d76373ed616ca34a422be80f</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-03-24</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>אופק יפרח אזולאי - עלם חמודות</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>אודיה - שיר לממ"ד</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-03-24</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410145&amp;sid=8b258206d76373ed616ca34a422be80f</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-03-24</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>אודיה - שיר לממ"ד</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L6"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-03-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-03-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>הודיה ויצמן - עכשיו בסדר</v>
+        <v>יוסי פריד - עבדים</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-24</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410149&amp;sid=8b258206d76373ed616ca34a422be80f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410153&amp;sid=33813398c9f0cdebd40374fdedc085f8</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-24</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>הודיה ויצמן - עכשיו בסדר</v>
+        <v>יוסי פריד - עבדים</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>אפיק מרחום - איתך הייתי פורח</v>
+        <v>יהודה שקד &amp; מלאכי יצחקי - ברוך אל עליון</v>
       </c>
       <c r="B3" t="str">
         <v>2026-03-24</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410148&amp;sid=8b258206d76373ed616ca34a422be80f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410152&amp;sid=33813398c9f0cdebd40374fdedc085f8</v>
       </c>
       <c r="D3" t="str">
         <v>2026-03-24</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>אפיק מרחום - איתך הייתי פורח</v>
+        <v>יהודה שקד &amp; מלאכי יצחקי - ברוך אל עליון</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>אלי וינר - אף פעם לא לבד</v>
+        <v>יהודה נר - כמה טוב</v>
       </c>
       <c r="B4" t="str">
         <v>2026-03-24</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410147&amp;sid=8b258206d76373ed616ca34a422be80f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410151&amp;sid=33813398c9f0cdebd40374fdedc085f8</v>
       </c>
       <c r="D4" t="str">
         <v>2026-03-24</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>אלי וינר - אף פעם לא לבד</v>
+        <v>יהודה נר - כמה טוב</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>אופק יפרח אזולאי - עלם חמודות</v>
+        <v>טוני ג'ינו - נשמה</v>
       </c>
       <c r="B5" t="str">
         <v>2026-03-24</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410146&amp;sid=8b258206d76373ed616ca34a422be80f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410150&amp;sid=33813398c9f0cdebd40374fdedc085f8</v>
       </c>
       <c r="D5" t="str">
         <v>2026-03-24</v>
@@ -583,50 +583,12 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>אופק יפרח אזולאי - עלם חמודות</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>אודיה - שיר לממ"ד</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-03-24</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410145&amp;sid=8b258206d76373ed616ca34a422be80f</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-03-24</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>אודיה - שיר לממ"ד</v>
+        <v>טוני ג'ינו - נשמה</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-03-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-03-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L12"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>יוסי פריד - עבדים</v>
+        <v>רויטל נחמני - מחרוזת אש 2026</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-24</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410153&amp;sid=33813398c9f0cdebd40374fdedc085f8</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410164&amp;sid=4e2b140fd071ec244e46ba2d7231e81b</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-24</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>יוסי פריד - עבדים</v>
+        <v>רויטל נחמני - מחרוזת אש 2026</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>יהודה שקד &amp; מלאכי יצחקי - ברוך אל עליון</v>
+        <v>ששון שאולוב - ציון</v>
       </c>
       <c r="B3" t="str">
         <v>2026-03-24</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410152&amp;sid=33813398c9f0cdebd40374fdedc085f8</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410163&amp;sid=4e2b140fd071ec244e46ba2d7231e81b</v>
       </c>
       <c r="D3" t="str">
         <v>2026-03-24</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>יהודה שקד &amp; מלאכי יצחקי - ברוך אל עליון</v>
+        <v>ששון שאולוב - ציון</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>יהודה נר - כמה טוב</v>
+        <v>שלום ממן - מחרוזת מרוקאית 2026</v>
       </c>
       <c r="B4" t="str">
         <v>2026-03-24</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410151&amp;sid=33813398c9f0cdebd40374fdedc085f8</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410162&amp;sid=4e2b140fd071ec244e46ba2d7231e81b</v>
       </c>
       <c r="D4" t="str">
         <v>2026-03-24</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>יהודה נר - כמה טוב</v>
+        <v>שלום ממן - מחרוזת מרוקאית 2026</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>טוני ג'ינו - נשמה</v>
+        <v>שלום ממן - יא בנתי בלאדי</v>
       </c>
       <c r="B5" t="str">
         <v>2026-03-24</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410150&amp;sid=33813398c9f0cdebd40374fdedc085f8</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410161&amp;sid=4e2b140fd071ec244e46ba2d7231e81b</v>
       </c>
       <c r="D5" t="str">
         <v>2026-03-24</v>
@@ -583,12 +583,278 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>טוני ג'ינו - נשמה</v>
+        <v>שלום ממן - יא בנתי בלאדי</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>רועי אדרי - תבואי אליי</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-03-24</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410160&amp;sid=4e2b140fd071ec244e46ba2d7231e81b</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-03-24</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>רועי אדרי - תבואי אליי</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>מיכאל בן שבת - דלת לליבך 2026</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-03-24</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410159&amp;sid=4e2b140fd071ec244e46ba2d7231e81b</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-03-24</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>מיכאל בן שבת - דלת לליבך 2026</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>קובי פרץ - הלב לא שוכח</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-03-24</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410158&amp;sid=4e2b140fd071ec244e46ba2d7231e81b</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-03-24</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>קובי פרץ - הלב לא שוכח</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>עמנואל זאודה - תשמור עליי</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-03-24</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410157&amp;sid=4e2b140fd071ec244e46ba2d7231e81b</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-03-24</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>עמנואל זאודה - תשמור עליי</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>עדן חסון &amp; מתן לוי - עושה שלום</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-03-24</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410156&amp;sid=4e2b140fd071ec244e46ba2d7231e81b</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-03-24</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>עדן חסון &amp; מתן לוי - עושה שלום</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>נעם ישראל - סטלה ברומו</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-03-24</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410155&amp;sid=4e2b140fd071ec244e46ba2d7231e81b</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-03-24</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>נעם ישראל - סטלה ברומו</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>משה כורסיה - דגל על הגב</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-03-24</v>
+      </c>
+      <c r="C12" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410154&amp;sid=4e2b140fd071ec244e46ba2d7231e81b</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-03-24</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>משה כורסיה - דגל על הגב</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L12"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-03-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-03-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L16"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>רויטל נחמני - מחרוזת אש 2026</v>
+        <v>שמעון גרשון - זה הלב שלך</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410164&amp;sid=4e2b140fd071ec244e46ba2d7231e81b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410180&amp;sid=ff026e2d9334cd6db935265ed3449629</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>רויטל נחמני - מחרוזת אש 2026</v>
+        <v>שמעון גרשון - זה הלב שלך</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>ששון שאולוב - ציון</v>
+        <v>רינת בר - נפש תאומה</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410163&amp;sid=4e2b140fd071ec244e46ba2d7231e81b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410179&amp;sid=ff026e2d9334cd6db935265ed3449629</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>ששון שאולוב - ציון</v>
+        <v>רינת בר - נפש תאומה</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>שלום ממן - מחרוזת מרוקאית 2026</v>
+        <v>עתרת - געגוע</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410162&amp;sid=4e2b140fd071ec244e46ba2d7231e81b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410178&amp;sid=ff026e2d9334cd6db935265ed3449629</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>שלום ממן - מחרוזת מרוקאית 2026</v>
+        <v>עתרת - געגוע</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>שלום ממן - יא בנתי בלאדי</v>
+        <v>עומר ביטון - בבהילו יצאנו ממצרים</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410161&amp;sid=4e2b140fd071ec244e46ba2d7231e81b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410177&amp;sid=ff026e2d9334cd6db935265ed3449629</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>שלום ממן - יא בנתי בלאדי</v>
+        <v>עומר ביטון - בבהילו יצאנו ממצרים</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>רועי אדרי - תבואי אליי</v>
+        <v>נר &amp; נתן - תמיד איתך</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410160&amp;sid=4e2b140fd071ec244e46ba2d7231e81b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410176&amp;sid=ff026e2d9334cd6db935265ed3449629</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -621,21 +621,21 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>רועי אדרי - תבואי אליי</v>
+        <v>נר &amp; נתן - תמיד איתך</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>מיכאל בן שבת - דלת לליבך 2026</v>
+        <v>מושיק עפיה &amp; ישי סוויסה - פצצה לחיבורים</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410159&amp;sid=4e2b140fd071ec244e46ba2d7231e81b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410175&amp;sid=ff026e2d9334cd6db935265ed3449629</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -659,21 +659,21 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>מיכאל בן שבת - דלת לליבך 2026</v>
+        <v>מושיק עפיה &amp; ישי סוויסה - פצצה לחיבורים</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>קובי פרץ - הלב לא שוכח</v>
+        <v>יוחאי בן אב''י - אהבת עולם</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410158&amp;sid=4e2b140fd071ec244e46ba2d7231e81b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410174&amp;sid=ff026e2d9334cd6db935265ed3449629</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -697,21 +697,21 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>קובי פרץ - הלב לא שוכח</v>
+        <v>יוחאי בן אב''י - אהבת עולם</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>עמנואל זאודה - תשמור עליי</v>
+        <v>יהודה יפרח - מקום חדש</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410157&amp;sid=4e2b140fd071ec244e46ba2d7231e81b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410173&amp;sid=ff026e2d9334cd6db935265ed3449629</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -735,21 +735,21 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>עמנואל זאודה - תשמור עליי</v>
+        <v>יהודה יפרח - מקום חדש</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>עדן חסון &amp; מתן לוי - עושה שלום</v>
+        <v>בצלאל שמיר &amp; יוסף חיים של שמחות - מחרוזת פסח 2026</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410156&amp;sid=4e2b140fd071ec244e46ba2d7231e81b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410172&amp;sid=ff026e2d9334cd6db935265ed3449629</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -773,21 +773,21 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>עדן חסון &amp; מתן לוי - עושה שלום</v>
+        <v>בצלאל שמיר &amp; יוסף חיים של שמחות - מחרוזת פסח 2026</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>נעם ישראל - סטלה ברומו</v>
+        <v>דוד בודה &amp; שלום קדושים - מחרוזת תאמר לה 2026</v>
       </c>
       <c r="B11" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410155&amp;sid=4e2b140fd071ec244e46ba2d7231e81b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410171&amp;sid=ff026e2d9334cd6db935265ed3449629</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -811,21 +811,21 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>נעם ישראל - סטלה ברומו</v>
+        <v>דוד בודה &amp; שלום קדושים - מחרוזת תאמר לה 2026</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>משה כורסיה - דגל על הגב</v>
+        <v>בן צור - יש אמת אחת</v>
       </c>
       <c r="B12" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410154&amp;sid=4e2b140fd071ec244e46ba2d7231e81b</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410169&amp;sid=ff026e2d9334cd6db935265ed3449629</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-03-24</v>
+        <v>2026-03-25</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -849,12 +849,164 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>משה כורסיה - דגל על הגב</v>
+        <v>בן צור - יש אמת אחת</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>אלקנה אלפסי - לברוח ממני</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-03-25</v>
+      </c>
+      <c r="C13" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410168&amp;sid=ff026e2d9334cd6db935265ed3449629</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2026-03-25</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v>אלקנה אלפסי - לברוח ממני</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>איציק שריקי - מאושרת לעולם</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2026-03-25</v>
+      </c>
+      <c r="C14" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410167&amp;sid=ff026e2d9334cd6db935265ed3449629</v>
+      </c>
+      <c r="D14" t="str">
+        <v>2026-03-25</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v>איציק שריקי - מאושרת לעולם</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>אבישי &amp; גריימן (חן נאמן) - הר סיני</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2026-03-25</v>
+      </c>
+      <c r="C15" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410166&amp;sid=ff026e2d9334cd6db935265ed3449629</v>
+      </c>
+      <c r="D15" t="str">
+        <v>2026-03-25</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
+        <v>אבישי &amp; גריימן (חן נאמן) - הר סיני</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>אביב אזרד מארח את אורן תורג'מן - יתברך אל יהוד</v>
+      </c>
+      <c r="B16" t="str">
+        <v>2026-03-25</v>
+      </c>
+      <c r="C16" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410165&amp;sid=ff026e2d9334cd6db935265ed3449629</v>
+      </c>
+      <c r="D16" t="str">
+        <v>2026-03-25</v>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <v/>
+      </c>
+      <c r="L16" t="str">
+        <v>אביב אזרד מארח את אורן תורג'מן - יתברך אל יהוד</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L16"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-03-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-03-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:L10"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שמעון גרשון - זה הלב שלך</v>
+        <v>תמיר גל &amp; נטלי פרץ - אהבה אסורה &amp; נשבענו ביחד</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410180&amp;sid=ff026e2d9334cd6db935265ed3449629</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410189&amp;sid=7f81c23f720bac22e7eb57133ed3bef8</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שמעון גרשון - זה הלב שלך</v>
+        <v>תמיר גל &amp; נטלי פרץ - אהבה אסורה &amp; נשבענו ביחד</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>רינת בר - נפש תאומה</v>
+        <v>רון יוסף - גבר אמיתי</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410179&amp;sid=ff026e2d9334cd6db935265ed3449629</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410188&amp;sid=7f81c23f720bac22e7eb57133ed3bef8</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>רינת בר - נפש תאומה</v>
+        <v>רון יוסף - גבר אמיתי</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>עתרת - געגוע</v>
+        <v>קובי אפללו - שיר של אהבה</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410178&amp;sid=ff026e2d9334cd6db935265ed3449629</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410187&amp;sid=7f81c23f720bac22e7eb57133ed3bef8</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>עתרת - געגוע</v>
+        <v>קובי אפללו - שיר של אהבה</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>עומר ביטון - בבהילו יצאנו ממצרים</v>
+        <v>סטטיק &amp; עמיר בניון - היה לי חלום</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410177&amp;sid=ff026e2d9334cd6db935265ed3449629</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410186&amp;sid=7f81c23f720bac22e7eb57133ed3bef8</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>עומר ביטון - בבהילו יצאנו ממצרים</v>
+        <v>סטטיק &amp; עמיר בניון - היה לי חלום</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>נר &amp; נתן - תמיד איתך</v>
+        <v>ליאור ביטון - ג׳יבואה לערוסה</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410176&amp;sid=ff026e2d9334cd6db935265ed3449629</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410185&amp;sid=7f81c23f720bac22e7eb57133ed3bef8</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -621,21 +621,21 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>נר &amp; נתן - תמיד איתך</v>
+        <v>ליאור ביטון - ג׳יבואה לערוסה</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>מושיק עפיה &amp; ישי סוויסה - פצצה לחיבורים</v>
+        <v>היוצרים - אבא</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410175&amp;sid=ff026e2d9334cd6db935265ed3449629</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410184&amp;sid=7f81c23f720bac22e7eb57133ed3bef8</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -659,21 +659,21 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>מושיק עפיה &amp; ישי סוויסה - פצצה לחיבורים</v>
+        <v>היוצרים - אבא</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>יוחאי בן אב''י - אהבת עולם</v>
+        <v>אלייצור &amp; בר קופרשטיין - המלחמה האחרונה</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410174&amp;sid=ff026e2d9334cd6db935265ed3449629</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410183&amp;sid=7f81c23f720bac22e7eb57133ed3bef8</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -697,21 +697,21 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>יוחאי בן אב''י - אהבת עולם</v>
+        <v>אלייצור &amp; בר קופרשטיין - המלחמה האחרונה</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>יהודה יפרח - מקום חדש</v>
+        <v>אליאור זנדני - מיליון מילים</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410173&amp;sid=ff026e2d9334cd6db935265ed3449629</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410182&amp;sid=7f81c23f720bac22e7eb57133ed3bef8</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -735,21 +735,21 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>יהודה יפרח - מקום חדש</v>
+        <v>אליאור זנדני - מיליון מילים</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>בצלאל שמיר &amp; יוסף חיים של שמחות - מחרוזת פסח 2026</v>
+        <v>אודי צברי - אין לי יום</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410172&amp;sid=ff026e2d9334cd6db935265ed3449629</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410181&amp;sid=7f81c23f720bac22e7eb57133ed3bef8</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-26</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -773,240 +773,12 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>בצלאל שמיר &amp; יוסף חיים של שמחות - מחרוזת פסח 2026</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>דוד בודה &amp; שלום קדושים - מחרוזת תאמר לה 2026</v>
-      </c>
-      <c r="B11" t="str">
-        <v>2026-03-25</v>
-      </c>
-      <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410171&amp;sid=ff026e2d9334cd6db935265ed3449629</v>
-      </c>
-      <c r="D11" t="str">
-        <v>2026-03-25</v>
-      </c>
-      <c r="E11" t="str">
-        <v/>
-      </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
-      <c r="G11" t="str">
-        <v/>
-      </c>
-      <c r="H11" t="str">
-        <v/>
-      </c>
-      <c r="I11" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J11" t="str">
-        <v/>
-      </c>
-      <c r="K11" t="str">
-        <v/>
-      </c>
-      <c r="L11" t="str">
-        <v>דוד בודה &amp; שלום קדושים - מחרוזת תאמר לה 2026</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>בן צור - יש אמת אחת</v>
-      </c>
-      <c r="B12" t="str">
-        <v>2026-03-25</v>
-      </c>
-      <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410169&amp;sid=ff026e2d9334cd6db935265ed3449629</v>
-      </c>
-      <c r="D12" t="str">
-        <v>2026-03-25</v>
-      </c>
-      <c r="E12" t="str">
-        <v/>
-      </c>
-      <c r="F12" t="str">
-        <v/>
-      </c>
-      <c r="G12" t="str">
-        <v/>
-      </c>
-      <c r="H12" t="str">
-        <v/>
-      </c>
-      <c r="I12" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J12" t="str">
-        <v/>
-      </c>
-      <c r="K12" t="str">
-        <v/>
-      </c>
-      <c r="L12" t="str">
-        <v>בן צור - יש אמת אחת</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>אלקנה אלפסי - לברוח ממני</v>
-      </c>
-      <c r="B13" t="str">
-        <v>2026-03-25</v>
-      </c>
-      <c r="C13" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410168&amp;sid=ff026e2d9334cd6db935265ed3449629</v>
-      </c>
-      <c r="D13" t="str">
-        <v>2026-03-25</v>
-      </c>
-      <c r="E13" t="str">
-        <v/>
-      </c>
-      <c r="F13" t="str">
-        <v/>
-      </c>
-      <c r="G13" t="str">
-        <v/>
-      </c>
-      <c r="H13" t="str">
-        <v/>
-      </c>
-      <c r="I13" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J13" t="str">
-        <v/>
-      </c>
-      <c r="K13" t="str">
-        <v/>
-      </c>
-      <c r="L13" t="str">
-        <v>אלקנה אלפסי - לברוח ממני</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>איציק שריקי - מאושרת לעולם</v>
-      </c>
-      <c r="B14" t="str">
-        <v>2026-03-25</v>
-      </c>
-      <c r="C14" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410167&amp;sid=ff026e2d9334cd6db935265ed3449629</v>
-      </c>
-      <c r="D14" t="str">
-        <v>2026-03-25</v>
-      </c>
-      <c r="E14" t="str">
-        <v/>
-      </c>
-      <c r="F14" t="str">
-        <v/>
-      </c>
-      <c r="G14" t="str">
-        <v/>
-      </c>
-      <c r="H14" t="str">
-        <v/>
-      </c>
-      <c r="I14" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J14" t="str">
-        <v/>
-      </c>
-      <c r="K14" t="str">
-        <v/>
-      </c>
-      <c r="L14" t="str">
-        <v>איציק שריקי - מאושרת לעולם</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>אבישי &amp; גריימן (חן נאמן) - הר סיני</v>
-      </c>
-      <c r="B15" t="str">
-        <v>2026-03-25</v>
-      </c>
-      <c r="C15" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410166&amp;sid=ff026e2d9334cd6db935265ed3449629</v>
-      </c>
-      <c r="D15" t="str">
-        <v>2026-03-25</v>
-      </c>
-      <c r="E15" t="str">
-        <v/>
-      </c>
-      <c r="F15" t="str">
-        <v/>
-      </c>
-      <c r="G15" t="str">
-        <v/>
-      </c>
-      <c r="H15" t="str">
-        <v/>
-      </c>
-      <c r="I15" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J15" t="str">
-        <v/>
-      </c>
-      <c r="K15" t="str">
-        <v/>
-      </c>
-      <c r="L15" t="str">
-        <v>אבישי &amp; גריימן (חן נאמן) - הר סיני</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>אביב אזרד מארח את אורן תורג'מן - יתברך אל יהוד</v>
-      </c>
-      <c r="B16" t="str">
-        <v>2026-03-25</v>
-      </c>
-      <c r="C16" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410165&amp;sid=ff026e2d9334cd6db935265ed3449629</v>
-      </c>
-      <c r="D16" t="str">
-        <v>2026-03-25</v>
-      </c>
-      <c r="E16" t="str">
-        <v/>
-      </c>
-      <c r="F16" t="str">
-        <v/>
-      </c>
-      <c r="G16" t="str">
-        <v/>
-      </c>
-      <c r="H16" t="str">
-        <v/>
-      </c>
-      <c r="I16" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J16" t="str">
-        <v/>
-      </c>
-      <c r="K16" t="str">
-        <v/>
-      </c>
-      <c r="L16" t="str">
-        <v>אביב אזרד מארח את אורן תורג'מן - יתברך אל יהוד</v>
+        <v>אודי צברי - אין לי יום</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L10"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-03-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-03-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>תמיר גל &amp; נטלי פרץ - אהבה אסורה &amp; נשבענו ביחד</v>
+        <v>שי חזן - מחרוזת שנות ה 90 2026</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410189&amp;sid=7f81c23f720bac22e7eb57133ed3bef8</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410204&amp;sid=cc54769106cc1e38d867c12e01d55af1</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>תמיר גל &amp; נטלי פרץ - אהבה אסורה &amp; נשבענו ביחד</v>
+        <v>שי חזן - מחרוזת שנות ה 90 2026</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>רון יוסף - גבר אמיתי</v>
+        <v>רפאל מלול - בכל דור ודור קאבר</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410188&amp;sid=7f81c23f720bac22e7eb57133ed3bef8</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410203&amp;sid=cc54769106cc1e38d867c12e01d55af1</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>רון יוסף - גבר אמיתי</v>
+        <v>רפאל מלול - בכל דור ודור קאבר</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>קובי אפללו - שיר של אהבה</v>
+        <v>פינחס מלך כהן - חלק ממך</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410187&amp;sid=7f81c23f720bac22e7eb57133ed3bef8</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410202&amp;sid=cc54769106cc1e38d867c12e01d55af1</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>קובי אפללו - שיר של אהבה</v>
+        <v>פינחס מלך כהן - חלק ממך</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>סטטיק &amp; עמיר בניון - היה לי חלום</v>
+        <v>נשמה וקצב - החצי שלך</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410186&amp;sid=7f81c23f720bac22e7eb57133ed3bef8</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410201&amp;sid=cc54769106cc1e38d867c12e01d55af1</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>סטטיק &amp; עמיר בניון - היה לי חלום</v>
+        <v>נשמה וקצב - החצי שלך</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>ליאור ביטון - ג׳יבואה לערוסה</v>
+        <v>נועם צוריאלי - צאי כבר</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410185&amp;sid=7f81c23f720bac22e7eb57133ed3bef8</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410200&amp;sid=cc54769106cc1e38d867c12e01d55af1</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -621,21 +621,21 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>ליאור ביטון - ג׳יבואה לערוסה</v>
+        <v>נועם צוריאלי - צאי כבר</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>היוצרים - אבא</v>
+        <v>חביב שאשא - שאת הולכת</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410184&amp;sid=7f81c23f720bac22e7eb57133ed3bef8</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410199&amp;sid=cc54769106cc1e38d867c12e01d55af1</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -659,21 +659,21 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>היוצרים - אבא</v>
+        <v>חביב שאשא - שאת הולכת</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>אלייצור &amp; בר קופרשטיין - המלחמה האחרונה</v>
+        <v>מאיה דדון &amp; גולדבאום - מה נשתנה</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410183&amp;sid=7f81c23f720bac22e7eb57133ed3bef8</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410198&amp;sid=cc54769106cc1e38d867c12e01d55af1</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -697,21 +697,21 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>אלייצור &amp; בר קופרשטיין - המלחמה האחרונה</v>
+        <v>מאיה דדון &amp; גולדבאום - מה נשתנה</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>אליאור זנדני - מיליון מילים</v>
+        <v>יהודה אביאל - מחרוזת מאוהב בגשם 2026</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410182&amp;sid=7f81c23f720bac22e7eb57133ed3bef8</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410197&amp;sid=cc54769106cc1e38d867c12e01d55af1</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -735,21 +735,21 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>אליאור זנדני - מיליון מילים</v>
+        <v>יהודה אביאל - מחרוזת מאוהב בגשם 2026</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>אודי צברי - אין לי יום</v>
+        <v>מאי קריטי &amp; אלי בן חמו - מחרוזת פעם בחיים 2026</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410181&amp;sid=7f81c23f720bac22e7eb57133ed3bef8</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410196&amp;sid=cc54769106cc1e38d867c12e01d55af1</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-03-26</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -773,12 +773,202 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>אודי צברי - אין לי יום</v>
+        <v>מאי קריטי &amp; אלי בן חמו - מחרוזת פעם בחיים 2026</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>יניב בן ישי - רואה אותך</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-03-27</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410195&amp;sid=cc54769106cc1e38d867c12e01d55af1</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-03-27</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>יניב בן ישי - רואה אותך</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>חן אלדטוב - קפה שחור</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-03-27</v>
+      </c>
+      <c r="C12" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410194&amp;sid=cc54769106cc1e38d867c12e01d55af1</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-03-27</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>חן אלדטוב - קפה שחור</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>היוצרים - אל תגיד אוף תגיד פרק ק</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-03-27</v>
+      </c>
+      <c r="C13" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410193&amp;sid=cc54769106cc1e38d867c12e01d55af1</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2026-03-27</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v>היוצרים - אל תגיד אוף תגיד פרק ק</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>אדיר אליה - אין לנו יותר סיכוי</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2026-03-27</v>
+      </c>
+      <c r="C14" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410192&amp;sid=cc54769106cc1e38d867c12e01d55af1</v>
+      </c>
+      <c r="D14" t="str">
+        <v>2026-03-27</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v>אדיר אליה - אין לנו יותר סיכוי</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>אבי ריימי &amp; יאיר בודנר מארחים את ביני לנדאו - יְדִיד נֶפֶשׁ</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2026-03-27</v>
+      </c>
+      <c r="C15" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410191&amp;sid=cc54769106cc1e38d867c12e01d55af1</v>
+      </c>
+      <c r="D15" t="str">
+        <v>2026-03-27</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
+        <v>אבי ריימי &amp; יאיר בודנר מארחים את ביני לנדאו - יְדִיד נֶפֶשׁ</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L15"/>
   </ignoredErrors>
 </worksheet>
 </file>